--- a/artfynd/A 65464-2021 artfynd.xlsx
+++ b/artfynd/A 65464-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY61"/>
+  <dimension ref="A1:AY62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115984595</v>
+        <v>115984572</v>
       </c>
       <c r="B2" t="n">
-        <v>90783</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92123</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>48</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>526714</v>
+        <v>526746</v>
       </c>
       <c r="R2" t="n">
-        <v>7264534</v>
+        <v>7264564</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -764,7 +759,7 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>3750</t>
+          <t>3782</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -786,37 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115984746</v>
+        <v>115984592</v>
       </c>
       <c r="B3" t="n">
-        <v>90306</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>526796</v>
+        <v>526810</v>
       </c>
       <c r="R3" t="n">
-        <v>7264384</v>
+        <v>7264536</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -875,7 +865,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>3775</t>
+          <t>3794</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -886,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mika Thunell</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -897,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115984645</v>
+        <v>115984723</v>
       </c>
       <c r="B4" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,39 +898,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gejmån - Ajaure, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>526541</v>
+        <v>526937</v>
       </c>
       <c r="R4" t="n">
-        <v>7264494</v>
+        <v>7264410</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -980,11 +960,6 @@
           <t>2022-10-10</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>förska hack</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -996,7 +971,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>3715</t>
+          <t>3833</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1007,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Mika Thunell</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1018,15 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115984724</v>
+        <v>115984565</v>
       </c>
       <c r="B5" t="n">
-        <v>90359</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1034,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1058,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>526776</v>
+        <v>526749</v>
       </c>
       <c r="R5" t="n">
-        <v>7264410</v>
+        <v>7264568</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1107,7 +1077,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>3781</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1118,7 +1088,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mika Thunell</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1129,37 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115984546</v>
+        <v>115984578</v>
       </c>
       <c r="B6" t="n">
-        <v>90783</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1169,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>526902</v>
+        <v>526897</v>
       </c>
       <c r="R6" t="n">
-        <v>7264577</v>
+        <v>7264552</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1218,7 +1183,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>3821</t>
+          <t>3823</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1240,15 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115984578</v>
+        <v>115984604</v>
       </c>
       <c r="B7" t="n">
-        <v>90624</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,12 +1225,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1280,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>526897</v>
+        <v>526714</v>
       </c>
       <c r="R7" t="n">
-        <v>7264552</v>
+        <v>7264529</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1329,7 +1289,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>3823</t>
+          <t>3751</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1351,15 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>115984700</v>
+        <v>115984627</v>
       </c>
       <c r="B8" t="n">
-        <v>90359</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,21 +1322,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1391,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>526565</v>
+        <v>526875</v>
       </c>
       <c r="R8" t="n">
-        <v>7264457</v>
+        <v>7264511</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1440,7 +1395,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>3716</t>
+          <t>3812</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1462,37 +1417,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115984572</v>
+        <v>115984650</v>
       </c>
       <c r="B9" t="n">
-        <v>90530</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>48</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1502,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>526746</v>
+        <v>526821</v>
       </c>
       <c r="R9" t="n">
-        <v>7264564</v>
+        <v>7264493</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1551,7 +1501,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>3782</t>
+          <t>3802</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1573,15 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>115984614</v>
+        <v>115984669</v>
       </c>
       <c r="B10" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1589,21 +1534,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1613,10 +1558,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>526853</v>
+        <v>526512</v>
       </c>
       <c r="R10" t="n">
-        <v>7264525</v>
+        <v>7264475</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1643,12 +1588,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
+          <t>2022-09-23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
+          <t>2022-09-23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1662,7 +1607,7 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>3810</t>
+          <t>3628</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1684,15 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>115984681</v>
+        <v>115984684</v>
       </c>
       <c r="B11" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1700,21 +1640,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1724,10 +1664,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>526681</v>
+        <v>526664</v>
       </c>
       <c r="R11" t="n">
-        <v>7264469</v>
+        <v>7264467</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1773,7 +1713,7 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>3737</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1795,15 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>115984729</v>
+        <v>115984686</v>
       </c>
       <c r="B12" t="n">
-        <v>90341</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>526784</v>
+        <v>526675</v>
       </c>
       <c r="R12" t="n">
-        <v>7264404</v>
+        <v>7264466</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1884,7 +1819,7 @@
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>3762</t>
+          <t>3747</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1895,7 +1830,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Mika Thunell</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1906,15 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>115984638</v>
+        <v>115984714</v>
       </c>
       <c r="B13" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1922,21 +1852,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1946,10 +1876,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>526497</v>
+        <v>526945</v>
       </c>
       <c r="R13" t="n">
-        <v>7264505</v>
+        <v>7264426</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1976,12 +1906,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-09-23</t>
+          <t>2022-10-10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-09-23</t>
+          <t>2022-10-10</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1995,7 +1925,7 @@
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>3814</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2006,7 +1936,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Mika Thunell</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2017,15 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>115984627</v>
+        <v>115984717</v>
       </c>
       <c r="B14" t="n">
-        <v>90624</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2042,12 +1967,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2057,10 +1982,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>526875</v>
+        <v>526874</v>
       </c>
       <c r="R14" t="n">
-        <v>7264511</v>
+        <v>7264422</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2106,7 +2031,7 @@
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>3812</t>
+          <t>3786</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2117,7 +2042,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Mika Thunell</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2128,15 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>115984728</v>
+        <v>115984718</v>
       </c>
       <c r="B15" t="n">
-        <v>90624</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2153,12 +2073,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2168,10 +2088,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>526845</v>
+        <v>527020</v>
       </c>
       <c r="R15" t="n">
-        <v>7264407</v>
+        <v>7264420</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2198,12 +2118,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
+          <t>2022-10-12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
+          <t>2022-10-12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2217,7 +2137,7 @@
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>3780</t>
+          <t>4494</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2228,7 +2148,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Mika Thunell</t>
+          <t>Erik Edvardsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2239,15 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>115984718</v>
+        <v>115984727</v>
       </c>
       <c r="B16" t="n">
-        <v>90624</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2264,12 +2179,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2279,10 +2194,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527020</v>
+        <v>526848</v>
       </c>
       <c r="R16" t="n">
-        <v>7264420</v>
+        <v>7264408</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2309,12 +2224,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-10-12</t>
+          <t>2022-10-10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-10-12</t>
+          <t>2022-10-10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2328,7 +2243,7 @@
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>4494</t>
+          <t>3783</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2339,7 +2254,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erik Edvardsson</t>
+          <t>Mika Thunell</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2350,15 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>115984669</v>
+        <v>115984728</v>
       </c>
       <c r="B17" t="n">
-        <v>90624</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2375,12 +2285,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2390,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>526512</v>
+        <v>526845</v>
       </c>
       <c r="R17" t="n">
-        <v>7264475</v>
+        <v>7264407</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2420,12 +2330,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-09-23</t>
+          <t>2022-10-10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-09-23</t>
+          <t>2022-10-10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2439,7 +2349,7 @@
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>3628</t>
+          <t>3780</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2450,7 +2360,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Mika Thunell</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2461,15 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>115984684</v>
+        <v>115984736</v>
       </c>
       <c r="B18" t="n">
-        <v>90624</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2486,12 +2391,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2501,10 +2406,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>526664</v>
+        <v>526784</v>
       </c>
       <c r="R18" t="n">
-        <v>7264467</v>
+        <v>7264401</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2550,7 +2455,7 @@
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>3737</t>
+          <t>3764</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2561,7 +2466,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Mika Thunell</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2572,15 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>115984717</v>
+        <v>115984749</v>
       </c>
       <c r="B19" t="n">
-        <v>90624</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2597,12 +2497,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2612,10 +2512,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>526874</v>
+        <v>526815</v>
       </c>
       <c r="R19" t="n">
-        <v>7264422</v>
+        <v>7264382</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2661,7 +2561,7 @@
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>3786</t>
+          <t>3777</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2683,15 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>115984680</v>
+        <v>115984766</v>
       </c>
       <c r="B20" t="n">
-        <v>90337</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2699,21 +2594,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2723,10 +2618,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>526684</v>
+        <v>526635</v>
       </c>
       <c r="R20" t="n">
-        <v>7264469</v>
+        <v>7264364</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2772,7 +2667,7 @@
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>3746</t>
+          <t>3727</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2783,7 +2678,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Mika Thunell</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2794,37 +2689,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>115984633</v>
+        <v>115984771</v>
       </c>
       <c r="B21" t="n">
-        <v>90783</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2834,10 +2724,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>526787</v>
+        <v>526642</v>
       </c>
       <c r="R21" t="n">
-        <v>7264510</v>
+        <v>7264360</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2883,7 +2773,7 @@
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>3788</t>
+          <t>3732</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2894,7 +2784,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Mika Thunell</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2905,37 +2795,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>115984685</v>
+        <v>115984611</v>
       </c>
       <c r="B22" t="n">
-        <v>90783</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2945,10 +2830,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>526653</v>
+        <v>526992</v>
       </c>
       <c r="R22" t="n">
-        <v>7264467</v>
+        <v>7264527</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2994,7 +2879,7 @@
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>3736</t>
+          <t>3830</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3019,12 +2904,7 @@
         <v>115984631</v>
       </c>
       <c r="B23" t="n">
-        <v>90337</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3127,15 +3007,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>115984761</v>
+        <v>115984680</v>
       </c>
       <c r="B24" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3143,21 +3018,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3167,10 +3042,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>526661</v>
+        <v>526684</v>
       </c>
       <c r="R24" t="n">
-        <v>7264373</v>
+        <v>7264469</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3216,7 +3091,7 @@
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>3743</t>
+          <t>3746</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3227,7 +3102,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Mika Thunell</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3238,15 +3113,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>115984712</v>
+        <v>115984626</v>
       </c>
       <c r="B25" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3254,39 +3124,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gejmån - Ajaure, Ly lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>527059</v>
+        <v>526724</v>
       </c>
       <c r="R25" t="n">
-        <v>7264440</v>
+        <v>7264512</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3313,17 +3178,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2022-10-12</t>
+          <t>2022-10-10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Hackmärken på gran</t>
+          <t>2022-10-10</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3337,7 +3197,7 @@
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>4495</t>
+          <t>3768</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3348,7 +3208,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Erik Edvardsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3359,15 +3219,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>115984565</v>
+        <v>115984632</v>
       </c>
       <c r="B26" t="n">
-        <v>90624</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3375,21 +3230,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3399,10 +3254,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>526749</v>
+        <v>526802</v>
       </c>
       <c r="R26" t="n">
-        <v>7264568</v>
+        <v>7264510</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3448,7 +3303,7 @@
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>3781</t>
+          <t>3792</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3470,15 +3325,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>115984632</v>
+        <v>115984722</v>
       </c>
       <c r="B27" t="n">
-        <v>90341</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3510,10 +3360,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>526802</v>
+        <v>526853</v>
       </c>
       <c r="R27" t="n">
-        <v>7264510</v>
+        <v>7264413</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3559,7 +3409,7 @@
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>3792</t>
+          <t>3784</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3570,7 +3420,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Mika Thunell</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3581,15 +3431,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>115984731</v>
+        <v>115984729</v>
       </c>
       <c r="B28" t="n">
-        <v>90359</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3597,21 +3442,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3621,10 +3466,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>526894</v>
+        <v>526784</v>
       </c>
       <c r="R28" t="n">
-        <v>7264402</v>
+        <v>7264404</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3670,7 +3515,7 @@
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>3806</t>
+          <t>3762</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3692,37 +3537,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>115984665</v>
+        <v>115984752</v>
       </c>
       <c r="B29" t="n">
-        <v>90783</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3732,10 +3572,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>526709</v>
+        <v>526818</v>
       </c>
       <c r="R29" t="n">
-        <v>7264483</v>
+        <v>7264381</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3781,7 +3621,7 @@
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>3773</t>
+          <t>3778</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3792,7 +3632,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Mika Thunell</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3803,15 +3643,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>115984727</v>
+        <v>115984764</v>
       </c>
       <c r="B30" t="n">
-        <v>90624</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3819,21 +3654,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3843,10 +3678,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>526848</v>
+        <v>526647</v>
       </c>
       <c r="R30" t="n">
-        <v>7264408</v>
+        <v>7264366</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3892,7 +3727,7 @@
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>3783</t>
+          <t>3733</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3914,37 +3749,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>115984686</v>
+        <v>115984652</v>
       </c>
       <c r="B31" t="n">
-        <v>90624</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3954,10 +3784,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>526675</v>
+        <v>526714</v>
       </c>
       <c r="R31" t="n">
-        <v>7264466</v>
+        <v>7264492</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4003,7 +3833,7 @@
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>3747</t>
+          <t>3771</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4025,15 +3855,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>115984749</v>
+        <v>115984546</v>
       </c>
       <c r="B32" t="n">
-        <v>90624</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4041,21 +3866,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4065,10 +3890,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>526815</v>
+        <v>526902</v>
       </c>
       <c r="R32" t="n">
-        <v>7264382</v>
+        <v>7264577</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4114,7 +3939,7 @@
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>3777</t>
+          <t>3821</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4125,7 +3950,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Mika Thunell</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4136,37 +3961,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>115984615</v>
+        <v>115984595</v>
       </c>
       <c r="B33" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3298</v>
+        <v>1209</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4176,10 +3996,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>526827</v>
+        <v>526714</v>
       </c>
       <c r="R33" t="n">
-        <v>7264525</v>
+        <v>7264534</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4225,7 +4045,7 @@
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>3796</t>
+          <t>3750</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4247,15 +4067,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>115984740</v>
+        <v>115984607</v>
       </c>
       <c r="B34" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4263,21 +4078,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4287,10 +4102,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>526752</v>
+        <v>526700</v>
       </c>
       <c r="R34" t="n">
-        <v>7264396</v>
+        <v>7264528</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4336,7 +4151,7 @@
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>3754</t>
+          <t>3748</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4347,7 +4162,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Mika Thunell</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4358,15 +4173,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>115984568</v>
+        <v>115984633</v>
       </c>
       <c r="B35" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4374,39 +4184,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Gejmån - Ajaure, Ly lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>526917</v>
+        <v>526787</v>
       </c>
       <c r="R35" t="n">
-        <v>7264567</v>
+        <v>7264510</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4441,11 +4246,6 @@
           <t>2022-10-10</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>hackmärken</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4457,7 +4257,7 @@
       </c>
       <c r="AR35" t="inlineStr">
         <is>
-          <t>3826</t>
+          <t>3788</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4479,37 +4279,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>115984672</v>
+        <v>115984637</v>
       </c>
       <c r="B36" t="n">
-        <v>91272</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4769</v>
+        <v>1209</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4519,10 +4314,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>526655</v>
+        <v>526713</v>
       </c>
       <c r="R36" t="n">
-        <v>7264472</v>
+        <v>7264505</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4568,7 +4363,7 @@
       </c>
       <c r="AR36" t="inlineStr">
         <is>
-          <t>3738</t>
+          <t>3757</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4590,15 +4385,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>115984722</v>
+        <v>115984665</v>
       </c>
       <c r="B37" t="n">
-        <v>90341</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4606,21 +4396,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4630,10 +4420,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>526853</v>
+        <v>526709</v>
       </c>
       <c r="R37" t="n">
-        <v>7264413</v>
+        <v>7264483</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4679,7 +4469,7 @@
       </c>
       <c r="AR37" t="inlineStr">
         <is>
-          <t>3784</t>
+          <t>3773</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4690,7 +4480,7 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Mika Thunell</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4701,15 +4491,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>115984592</v>
+        <v>115984685</v>
       </c>
       <c r="B38" t="n">
-        <v>95212</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4717,21 +4502,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>53</v>
+        <v>1209</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4741,10 +4526,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>526810</v>
+        <v>526653</v>
       </c>
       <c r="R38" t="n">
-        <v>7264536</v>
+        <v>7264467</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4790,7 +4575,7 @@
       </c>
       <c r="AR38" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>3736</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4812,15 +4597,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>115984650</v>
+        <v>115984681</v>
       </c>
       <c r="B39" t="n">
-        <v>90624</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4828,21 +4608,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4852,10 +4632,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>526821</v>
+        <v>526681</v>
       </c>
       <c r="R39" t="n">
-        <v>7264493</v>
+        <v>7264469</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4901,7 +4681,7 @@
       </c>
       <c r="AR39" t="inlineStr">
         <is>
-          <t>3802</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4923,37 +4703,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>115984596</v>
+        <v>115984721</v>
       </c>
       <c r="B40" t="n">
-        <v>97661</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219811</v>
+        <v>1312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4963,10 +4738,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>526589</v>
+        <v>526978</v>
       </c>
       <c r="R40" t="n">
-        <v>7264534</v>
+        <v>7264413</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5012,7 +4787,7 @@
       </c>
       <c r="AR40" t="inlineStr">
         <is>
-          <t>3729</t>
+          <t>3828</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5023,7 +4798,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Mika Thunell</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -5034,37 +4809,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>115984637</v>
+        <v>115984615</v>
       </c>
       <c r="B41" t="n">
-        <v>90783</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1209</v>
+        <v>3298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5074,10 +4844,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>526713</v>
+        <v>526827</v>
       </c>
       <c r="R41" t="n">
-        <v>7264505</v>
+        <v>7264525</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5123,7 +4893,7 @@
       </c>
       <c r="AR41" t="inlineStr">
         <is>
-          <t>3757</t>
+          <t>3796</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5148,12 +4918,7 @@
         <v>115984664</v>
       </c>
       <c r="B42" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5256,37 +5021,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>115984752</v>
+        <v>115984691</v>
       </c>
       <c r="B43" t="n">
-        <v>90341</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>4217</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5296,10 +5056,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>526818</v>
+        <v>526513</v>
       </c>
       <c r="R43" t="n">
-        <v>7264381</v>
+        <v>7264464</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5345,7 +5105,7 @@
       </c>
       <c r="AR43" t="inlineStr">
         <is>
-          <t>3778</t>
+          <t>3708</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5356,7 +5116,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Mika Thunell</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5367,37 +5127,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>115984617</v>
+        <v>115984550</v>
       </c>
       <c r="B44" t="n">
-        <v>90359</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>4769</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5407,10 +5162,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>526906</v>
+        <v>526934</v>
       </c>
       <c r="R44" t="n">
-        <v>7264522</v>
+        <v>7264575</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5456,7 +5211,7 @@
       </c>
       <c r="AR44" t="inlineStr">
         <is>
-          <t>3818</t>
+          <t>3827</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5481,12 +5236,7 @@
         <v>115984654</v>
       </c>
       <c r="B45" t="n">
-        <v>91272</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5508,7 +5258,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5589,37 +5339,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>115984607</v>
+        <v>115984672</v>
       </c>
       <c r="B46" t="n">
-        <v>90783</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1209</v>
+        <v>4769</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5629,10 +5374,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>526700</v>
+        <v>526655</v>
       </c>
       <c r="R46" t="n">
-        <v>7264528</v>
+        <v>7264472</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5678,7 +5423,7 @@
       </c>
       <c r="AR46" t="inlineStr">
         <is>
-          <t>3748</t>
+          <t>3738</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5700,15 +5445,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>115984550</v>
+        <v>115984719</v>
       </c>
       <c r="B47" t="n">
-        <v>91272</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5730,7 +5470,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5740,10 +5480,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>526934</v>
+        <v>527013</v>
       </c>
       <c r="R47" t="n">
-        <v>7264575</v>
+        <v>7264420</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5770,12 +5510,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
+          <t>2022-10-12</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
+          <t>2022-10-12</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5789,7 +5529,7 @@
       </c>
       <c r="AR47" t="inlineStr">
         <is>
-          <t>3827</t>
+          <t>4482</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5800,7 +5540,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Erik Edvardsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5811,37 +5551,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>115984736</v>
+        <v>115984746</v>
       </c>
       <c r="B48" t="n">
-        <v>90624</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5851,10 +5586,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>526784</v>
+        <v>526796</v>
       </c>
       <c r="R48" t="n">
-        <v>7264401</v>
+        <v>7264384</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5900,7 +5635,7 @@
       </c>
       <c r="AR48" t="inlineStr">
         <is>
-          <t>3764</t>
+          <t>3775</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5922,37 +5657,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>115984714</v>
+        <v>115984597</v>
       </c>
       <c r="B49" t="n">
-        <v>90624</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5962,10 +5692,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>526945</v>
+        <v>526574</v>
       </c>
       <c r="R49" t="n">
-        <v>7264426</v>
+        <v>7264534</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6011,7 +5741,7 @@
       </c>
       <c r="AR49" t="inlineStr">
         <is>
-          <t>3814</t>
+          <t>3728</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6022,7 +5752,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Mika Thunell</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -6033,37 +5763,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>115984723</v>
+        <v>115984614</v>
       </c>
       <c r="B50" t="n">
-        <v>86661</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6073,10 +5798,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>526937</v>
+        <v>526853</v>
       </c>
       <c r="R50" t="n">
-        <v>7264410</v>
+        <v>7264525</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6122,7 +5847,7 @@
       </c>
       <c r="AR50" t="inlineStr">
         <is>
-          <t>3833</t>
+          <t>3810</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6133,7 +5858,7 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Mika Thunell</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -6144,37 +5869,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>115984764</v>
+        <v>115984638</v>
       </c>
       <c r="B51" t="n">
-        <v>90341</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6184,10 +5904,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>526647</v>
+        <v>526497</v>
       </c>
       <c r="R51" t="n">
-        <v>7264366</v>
+        <v>7264505</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6214,12 +5934,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
+          <t>2022-09-23</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
+          <t>2022-09-23</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6233,7 +5953,7 @@
       </c>
       <c r="AR51" t="inlineStr">
         <is>
-          <t>3733</t>
+          <t>3642</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6244,7 +5964,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Mika Thunell</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -6255,37 +5975,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>115984666</v>
+        <v>115984740</v>
       </c>
       <c r="B52" t="n">
-        <v>90359</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6295,10 +6010,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>526521</v>
+        <v>526752</v>
       </c>
       <c r="R52" t="n">
-        <v>7264482</v>
+        <v>7264396</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6344,7 +6059,7 @@
       </c>
       <c r="AR52" t="inlineStr">
         <is>
-          <t>3710</t>
+          <t>3754</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6355,7 +6070,7 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Mika Thunell</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6366,55 +6081,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>115984735</v>
+        <v>115984761</v>
       </c>
       <c r="B53" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Gejmån - Ajaure, Ly lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>526874</v>
+        <v>526661</v>
       </c>
       <c r="R53" t="n">
-        <v>7264401</v>
+        <v>7264373</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6460,7 +6165,7 @@
       </c>
       <c r="AR53" t="inlineStr">
         <is>
-          <t>3789</t>
+          <t>3743</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6482,50 +6187,54 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>115984652</v>
+        <v>115984636</v>
       </c>
       <c r="B54" t="n">
-        <v>90355</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1204</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Gejmån - Ajaure, Ly lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>526714</v>
+        <v>526522</v>
       </c>
       <c r="R54" t="n">
-        <v>7264492</v>
+        <v>7264508</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6571,7 +6280,7 @@
       </c>
       <c r="AR54" t="inlineStr">
         <is>
-          <t>3771</t>
+          <t>3703</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6593,15 +6302,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>115984604</v>
+        <v>115984568</v>
       </c>
       <c r="B55" t="n">
-        <v>90624</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6609,34 +6313,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Gejmån - Ajaure, Ly lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>526714</v>
+        <v>526917</v>
       </c>
       <c r="R55" t="n">
-        <v>7264529</v>
+        <v>7264567</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6671,6 +6380,11 @@
           <t>2022-10-10</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>hackmärken</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6682,7 +6396,7 @@
       </c>
       <c r="AR55" t="inlineStr">
         <is>
-          <t>3751</t>
+          <t>3826</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6704,50 +6418,50 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>115984719</v>
+        <v>115984645</v>
       </c>
       <c r="B56" t="n">
-        <v>91272</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Gejmån - Ajaure, Ly lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>527013</v>
+        <v>526541</v>
       </c>
       <c r="R56" t="n">
-        <v>7264420</v>
+        <v>7264494</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6774,12 +6488,17 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2022-10-12</t>
+          <t>2022-10-10</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2022-10-12</t>
+          <t>2022-10-10</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>förska hack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6793,7 +6512,7 @@
       </c>
       <c r="AR56" t="inlineStr">
         <is>
-          <t>4482</t>
+          <t>3715</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -6804,7 +6523,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Erik Edvardsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6815,15 +6534,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>115984721</v>
+        <v>115984712</v>
       </c>
       <c r="B57" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6831,34 +6545,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Gejmån - Ajaure, Ly lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>526978</v>
+        <v>527059</v>
       </c>
       <c r="R57" t="n">
-        <v>7264413</v>
+        <v>7264440</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6885,12 +6604,17 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
+          <t>2022-10-12</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
+          <t>2022-10-12</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Hackmärken på gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6904,7 +6628,7 @@
       </c>
       <c r="AR57" t="inlineStr">
         <is>
-          <t>3828</t>
+          <t>4495</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -6915,7 +6639,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Mika Thunell</t>
+          <t>Erik Edvardsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6926,43 +6650,38 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>115984621</v>
+        <v>115984735</v>
       </c>
       <c r="B58" t="n">
-        <v>5165</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -6971,10 +6690,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>526495</v>
+        <v>526874</v>
       </c>
       <c r="R58" t="n">
-        <v>7264519</v>
+        <v>7264401</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7001,12 +6720,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2022-09-23</t>
+          <t>2022-10-10</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2022-09-23</t>
+          <t>2022-10-10</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7020,7 +6739,7 @@
       </c>
       <c r="AR58" t="inlineStr">
         <is>
-          <t>3643</t>
+          <t>3789</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7031,7 +6750,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Mika Thunell</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -7042,15 +6761,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>115984636</v>
+        <v>115984755</v>
       </c>
       <c r="B59" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7058,16 +6772,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -7075,14 +6789,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7091,10 +6801,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>526522</v>
+        <v>526603</v>
       </c>
       <c r="R59" t="n">
-        <v>7264508</v>
+        <v>7264379</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7140,7 +6850,7 @@
       </c>
       <c r="AR59" t="inlineStr">
         <is>
-          <t>3703</t>
+          <t>3705</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7151,7 +6861,7 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Mika Thunell</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -7162,15 +6872,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>115984691</v>
+        <v>115984621</v>
       </c>
       <c r="B60" t="n">
-        <v>90735</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7178,34 +6883,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4217</v>
+        <v>100526</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Gejmån - Ajaure, Ly lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>526513</v>
+        <v>526495</v>
       </c>
       <c r="R60" t="n">
-        <v>7264464</v>
+        <v>7264519</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7232,12 +6942,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
+          <t>2022-09-23</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
+          <t>2022-09-23</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7251,7 +6961,7 @@
       </c>
       <c r="AR60" t="inlineStr">
         <is>
-          <t>3708</t>
+          <t>3643</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7273,15 +6983,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>115984626</v>
+        <v>115984573</v>
       </c>
       <c r="B61" t="n">
-        <v>90341</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7289,34 +6994,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>103031</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Gejmån - Ajaure, Ly lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>526724</v>
+        <v>526981</v>
       </c>
       <c r="R61" t="n">
-        <v>7264512</v>
+        <v>7264563</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7351,6 +7061,11 @@
           <t>2022-10-10</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>hörd</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -7362,7 +7077,7 @@
       </c>
       <c r="AR61" t="inlineStr">
         <is>
-          <t>3768</t>
+          <t>3831</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7377,6 +7092,112 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr">
+        <is>
+          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>115984596</v>
+      </c>
+      <c r="B62" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Gejmån - Ajaure, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>526589</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7264534</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2022-10-10</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2022-10-10</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>3729</t>
+        </is>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Rickard Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
         <is>
           <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
         </is>
